--- a/copd/feedback/live.xlsx
+++ b/copd/feedback/live.xlsx
@@ -380,9 +380,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Useful</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Suggestion</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-31T15:52:45Z</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>copd S33US7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Useful</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Really useful, thank you.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-31T15:54:42Z</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>copd S33US7</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Useful</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Thanks for a really useful presentation.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Heart failure</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-31T15:54:42Z</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>copd S33US7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Useful</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thanks, good reminder of the pitfalls of reliance on NEWS2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>